--- a/data/삼성물산_일별_기준주가.xlsx
+++ b/data/삼성물산_일별_기준주가.xlsx
@@ -11285,25 +11285,25 @@
         <v>46283</v>
       </c>
       <c r="B419" t="n">
-        <v>353500</v>
+        <v>351000</v>
       </c>
       <c r="C419" t="n">
-        <v>115890</v>
+        <v>317618</v>
       </c>
       <c r="D419" t="n">
-        <v>350763</v>
+        <v>350750</v>
       </c>
       <c r="E419" t="n">
-        <v>372580</v>
+        <v>372018</v>
       </c>
       <c r="F419" t="n">
-        <v>353540</v>
+        <v>352925</v>
       </c>
       <c r="G419" t="n">
-        <v>358961</v>
+        <v>358564</v>
       </c>
       <c r="H419" t="n">
-        <v>0.8663612919326997</v>
+        <v>0.8642971528398811</v>
       </c>
     </row>
   </sheetData>

--- a/data/삼성물산_일별_기준주가.xlsx
+++ b/data/삼성물산_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H419"/>
+  <dimension ref="A1:H420"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11306,6 +11306,32 @@
         <v>0.8642971528398811</v>
       </c>
     </row>
+    <row r="420">
+      <c r="A420" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B420" t="n">
+        <v>367500</v>
+      </c>
+      <c r="C420" t="n">
+        <v>307373</v>
+      </c>
+      <c r="D420" t="n">
+        <v>352581</v>
+      </c>
+      <c r="E420" t="n">
+        <v>370756</v>
+      </c>
+      <c r="F420" t="n">
+        <v>355073</v>
+      </c>
+      <c r="G420" t="n">
+        <v>359470</v>
+      </c>
+      <c r="H420" t="n">
+        <v>0.8690077574194621</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성물산_일별_기준주가.xlsx
+++ b/data/삼성물산_일별_기준주가.xlsx
@@ -11337,25 +11337,25 @@
         <v>46287</v>
       </c>
       <c r="B421" t="n">
-        <v>371500</v>
+        <v>367000</v>
       </c>
       <c r="C421" t="n">
-        <v>49843</v>
+        <v>260132</v>
       </c>
       <c r="D421" t="n">
-        <v>352591</v>
+        <v>352753</v>
       </c>
       <c r="E421" t="n">
-        <v>370761</v>
+        <v>370626</v>
       </c>
       <c r="F421" t="n">
-        <v>357887</v>
+        <v>359193</v>
       </c>
       <c r="G421" t="n">
-        <v>360413</v>
+        <v>360857</v>
       </c>
       <c r="H421" t="n">
-        <v>0.8739107376827568</v>
+        <v>0.8762192458873199</v>
       </c>
     </row>
   </sheetData>

--- a/data/삼성물산_일별_기준주가.xlsx
+++ b/data/삼성물산_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H421"/>
+  <dimension ref="A1:H422"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11358,6 +11358,32 @@
         <v>0.8762192458873199</v>
       </c>
     </row>
+    <row r="422">
+      <c r="A422" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B422" t="n">
+        <v>367000</v>
+      </c>
+      <c r="C422" t="n">
+        <v>270617</v>
+      </c>
+      <c r="D422" t="n">
+        <v>352828</v>
+      </c>
+      <c r="E422" t="n">
+        <v>370500</v>
+      </c>
+      <c r="F422" t="n">
+        <v>361771</v>
+      </c>
+      <c r="G422" t="n">
+        <v>361700</v>
+      </c>
+      <c r="H422" t="n">
+        <v>0.8806022918703076</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성물산_일별_기준주가.xlsx
+++ b/data/삼성물산_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H422"/>
+  <dimension ref="A1:H423"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11384,6 +11384,32 @@
         <v>0.8806022918703076</v>
       </c>
     </row>
+    <row r="423">
+      <c r="A423" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B423" t="n">
+        <v>345500</v>
+      </c>
+      <c r="C423" t="n">
+        <v>495182</v>
+      </c>
+      <c r="D423" t="n">
+        <v>354898</v>
+      </c>
+      <c r="E423" t="n">
+        <v>367745</v>
+      </c>
+      <c r="F423" t="n">
+        <v>357566</v>
+      </c>
+      <c r="G423" t="n">
+        <v>360070</v>
+      </c>
+      <c r="H423" t="n">
+        <v>0.872127363101304</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성물산_일별_기준주가.xlsx
+++ b/data/삼성물산_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H423"/>
+  <dimension ref="A1:H424"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11410,6 +11410,32 @@
         <v>0.872127363101304</v>
       </c>
     </row>
+    <row r="424">
+      <c r="A424" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B424" t="n">
+        <v>345000</v>
+      </c>
+      <c r="C424" t="n">
+        <v>265768</v>
+      </c>
+      <c r="D424" t="n">
+        <v>358572</v>
+      </c>
+      <c r="E424" t="n">
+        <v>366828</v>
+      </c>
+      <c r="F424" t="n">
+        <v>356782</v>
+      </c>
+      <c r="G424" t="n">
+        <v>360727</v>
+      </c>
+      <c r="H424" t="n">
+        <v>0.8755433313229208</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성물산_일별_기준주가.xlsx
+++ b/data/삼성물산_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H424"/>
+  <dimension ref="A1:H425"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11436,6 +11436,32 @@
         <v>0.8755433313229208</v>
       </c>
     </row>
+    <row r="425">
+      <c r="A425" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B425" t="n">
+        <v>341500</v>
+      </c>
+      <c r="C425" t="n">
+        <v>282214</v>
+      </c>
+      <c r="D425" t="n">
+        <v>362765</v>
+      </c>
+      <c r="E425" t="n">
+        <v>365282</v>
+      </c>
+      <c r="F425" t="n">
+        <v>351948</v>
+      </c>
+      <c r="G425" t="n">
+        <v>359999</v>
+      </c>
+      <c r="H425" t="n">
+        <v>0.871758209762286</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성물산_일별_기준주가.xlsx
+++ b/data/삼성물산_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H425"/>
+  <dimension ref="A1:H427"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11462,6 +11462,58 @@
         <v>0.871758209762286</v>
       </c>
     </row>
+    <row r="426">
+      <c r="A426" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B426" t="n">
+        <v>347000</v>
+      </c>
+      <c r="C426" t="n">
+        <v>201309</v>
+      </c>
+      <c r="D426" t="n">
+        <v>362543</v>
+      </c>
+      <c r="E426" t="n">
+        <v>363538</v>
+      </c>
+      <c r="F426" t="n">
+        <v>348707</v>
+      </c>
+      <c r="G426" t="n">
+        <v>358263</v>
+      </c>
+      <c r="H426" t="n">
+        <v>0.8627321506561572</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B427" t="n">
+        <v>346000</v>
+      </c>
+      <c r="C427" t="n">
+        <v>224054</v>
+      </c>
+      <c r="D427" t="n">
+        <v>362288</v>
+      </c>
+      <c r="E427" t="n">
+        <v>362434</v>
+      </c>
+      <c r="F427" t="n">
+        <v>344923</v>
+      </c>
+      <c r="G427" t="n">
+        <v>356548</v>
+      </c>
+      <c r="H427" t="n">
+        <v>0.8538152777488925</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성물산_일별_기준주가.xlsx
+++ b/data/삼성물산_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H427"/>
+  <dimension ref="A1:H428"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11514,6 +11514,32 @@
         <v>0.8538152777488925</v>
       </c>
     </row>
+    <row r="428">
+      <c r="A428" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B428" t="n">
+        <v>342000</v>
+      </c>
+      <c r="C428" t="n">
+        <v>252936</v>
+      </c>
+      <c r="D428" t="n">
+        <v>365156</v>
+      </c>
+      <c r="E428" t="n">
+        <v>360754</v>
+      </c>
+      <c r="F428" t="n">
+        <v>344087</v>
+      </c>
+      <c r="G428" t="n">
+        <v>356665</v>
+      </c>
+      <c r="H428" t="n">
+        <v>0.8544236008568518</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성물산_일별_기준주가.xlsx
+++ b/data/삼성물산_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H428"/>
+  <dimension ref="A1:H429"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11540,6 +11540,32 @@
         <v>0.8544236008568518</v>
       </c>
     </row>
+    <row r="429">
+      <c r="A429" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B429" t="n">
+        <v>336000</v>
+      </c>
+      <c r="C429" t="n">
+        <v>239304</v>
+      </c>
+      <c r="D429" t="n">
+        <v>365209</v>
+      </c>
+      <c r="E429" t="n">
+        <v>358644</v>
+      </c>
+      <c r="F429" t="n">
+        <v>342272</v>
+      </c>
+      <c r="G429" t="n">
+        <v>355375</v>
+      </c>
+      <c r="H429" t="n">
+        <v>0.8477164486408917</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성물산_일별_기준주가.xlsx
+++ b/data/삼성물산_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H429"/>
+  <dimension ref="A1:H430"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11566,6 +11566,32 @@
         <v>0.8477164486408917</v>
       </c>
     </row>
+    <row r="430">
+      <c r="A430" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B430" t="n">
+        <v>317500</v>
+      </c>
+      <c r="C430" t="n">
+        <v>538853</v>
+      </c>
+      <c r="D430" t="n">
+        <v>363352</v>
+      </c>
+      <c r="E430" t="n">
+        <v>353393</v>
+      </c>
+      <c r="F430" t="n">
+        <v>333256</v>
+      </c>
+      <c r="G430" t="n">
+        <v>350000</v>
+      </c>
+      <c r="H430" t="n">
+        <v>0.8197699810743921</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성물산_일별_기준주가.xlsx
+++ b/data/삼성물산_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H430"/>
+  <dimension ref="A1:H431"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11592,6 +11592,32 @@
         <v>0.8197699810743921</v>
       </c>
     </row>
+    <row r="431">
+      <c r="A431" s="1" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B431" t="n">
+        <v>314500</v>
+      </c>
+      <c r="C431" t="n">
+        <v>328938</v>
+      </c>
+      <c r="D431" t="n">
+        <v>363332</v>
+      </c>
+      <c r="E431" t="n">
+        <v>345209</v>
+      </c>
+      <c r="F431" t="n">
+        <v>327615</v>
+      </c>
+      <c r="G431" t="n">
+        <v>345385</v>
+      </c>
+      <c r="H431" t="n">
+        <v>0.7957750140382256</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성물산_일별_기준주가.xlsx
+++ b/data/삼성물산_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H431"/>
+  <dimension ref="A1:H432"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11618,6 +11618,32 @@
         <v>0.7957750140382256</v>
       </c>
     </row>
+    <row r="432">
+      <c r="A432" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B432" t="n">
+        <v>300000</v>
+      </c>
+      <c r="C432" t="n">
+        <v>445467</v>
+      </c>
+      <c r="D432" t="n">
+        <v>361108</v>
+      </c>
+      <c r="E432" t="n">
+        <v>341490</v>
+      </c>
+      <c r="F432" t="n">
+        <v>318520</v>
+      </c>
+      <c r="G432" t="n">
+        <v>340373</v>
+      </c>
+      <c r="H432" t="n">
+        <v>0.7697159079092404</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성물산_일별_기준주가.xlsx
+++ b/data/삼성물산_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H432"/>
+  <dimension ref="A1:H433"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11644,6 +11644,32 @@
         <v>0.7697159079092404</v>
       </c>
     </row>
+    <row r="433">
+      <c r="A433" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B433" t="n">
+        <v>291500</v>
+      </c>
+      <c r="C433" t="n">
+        <v>500743</v>
+      </c>
+      <c r="D433" t="n">
+        <v>358321</v>
+      </c>
+      <c r="E433" t="n">
+        <v>336133</v>
+      </c>
+      <c r="F433" t="n">
+        <v>309038</v>
+      </c>
+      <c r="G433" t="n">
+        <v>334497</v>
+      </c>
+      <c r="H433" t="n">
+        <v>0.7391645695984028</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성물산_일별_기준주가.xlsx
+++ b/data/삼성물산_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H433"/>
+  <dimension ref="A1:H434"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11670,6 +11670,32 @@
         <v>0.7391645695984028</v>
       </c>
     </row>
+    <row r="434">
+      <c r="A434" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B434" t="n">
+        <v>267500</v>
+      </c>
+      <c r="C434" t="n">
+        <v>523477</v>
+      </c>
+      <c r="D434" t="n">
+        <v>354878</v>
+      </c>
+      <c r="E434" t="n">
+        <v>329494</v>
+      </c>
+      <c r="F434" t="n">
+        <v>296975</v>
+      </c>
+      <c r="G434" t="n">
+        <v>327116</v>
+      </c>
+      <c r="H434" t="n">
+        <v>0.7007882203689453</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성물산_일별_기준주가.xlsx
+++ b/data/삼성물산_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H434"/>
+  <dimension ref="A1:H435"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11696,6 +11696,32 @@
         <v>0.7007882203689453</v>
       </c>
     </row>
+    <row r="435">
+      <c r="A435" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B435" t="n">
+        <v>286500</v>
+      </c>
+      <c r="C435" t="n">
+        <v>585539</v>
+      </c>
+      <c r="D435" t="n">
+        <v>352098</v>
+      </c>
+      <c r="E435" t="n">
+        <v>324546</v>
+      </c>
+      <c r="F435" t="n">
+        <v>289764</v>
+      </c>
+      <c r="G435" t="n">
+        <v>322136</v>
+      </c>
+      <c r="H435" t="n">
+        <v>0.6748954932096582</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성물산_일별_기준주가.xlsx
+++ b/data/삼성물산_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H435"/>
+  <dimension ref="A1:H436"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11722,6 +11722,32 @@
         <v>0.6748954932096582</v>
       </c>
     </row>
+    <row r="436">
+      <c r="A436" s="1" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B436" t="n">
+        <v>285000</v>
+      </c>
+      <c r="C436" t="n">
+        <v>275397</v>
+      </c>
+      <c r="D436" t="n">
+        <v>350368</v>
+      </c>
+      <c r="E436" t="n">
+        <v>320411</v>
+      </c>
+      <c r="F436" t="n">
+        <v>285710</v>
+      </c>
+      <c r="G436" t="n">
+        <v>318829</v>
+      </c>
+      <c r="H436" t="n">
+        <v>0.6577012665599069</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성물산_일별_기준주가.xlsx
+++ b/data/삼성물산_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H436"/>
+  <dimension ref="A1:H437"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11748,6 +11748,32 @@
         <v>0.6577012665599069</v>
       </c>
     </row>
+    <row r="437">
+      <c r="A437" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B437" t="n">
+        <v>275000</v>
+      </c>
+      <c r="C437" t="n">
+        <v>281787</v>
+      </c>
+      <c r="D437" t="n">
+        <v>348034</v>
+      </c>
+      <c r="E437" t="n">
+        <v>318373</v>
+      </c>
+      <c r="F437" t="n">
+        <v>281379</v>
+      </c>
+      <c r="G437" t="n">
+        <v>315929</v>
+      </c>
+      <c r="H437" t="n">
+        <v>0.6426231724310048</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성물산_일별_기준주가.xlsx
+++ b/data/삼성물산_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H437"/>
+  <dimension ref="A1:H438"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11774,6 +11774,32 @@
         <v>0.6426231724310048</v>
       </c>
     </row>
+    <row r="438">
+      <c r="A438" s="1" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B438" t="n">
+        <v>290000</v>
+      </c>
+      <c r="C438" t="n">
+        <v>349511</v>
+      </c>
+      <c r="D438" t="n">
+        <v>344488</v>
+      </c>
+      <c r="E438" t="n">
+        <v>314415</v>
+      </c>
+      <c r="F438" t="n">
+        <v>280360</v>
+      </c>
+      <c r="G438" t="n">
+        <v>313088</v>
+      </c>
+      <c r="H438" t="n">
+        <v>0.6278518395274837</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성물산_일별_기준주가.xlsx
+++ b/data/삼성물산_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H438"/>
+  <dimension ref="A1:H439"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11800,6 +11800,32 @@
         <v>0.6278518395274837</v>
       </c>
     </row>
+    <row r="439">
+      <c r="A439" s="1" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B439" t="n">
+        <v>288500</v>
+      </c>
+      <c r="C439" t="n">
+        <v>481771</v>
+      </c>
+      <c r="D439" t="n">
+        <v>342567</v>
+      </c>
+      <c r="E439" t="n">
+        <v>310417</v>
+      </c>
+      <c r="F439" t="n">
+        <v>285757</v>
+      </c>
+      <c r="G439" t="n">
+        <v>312913</v>
+      </c>
+      <c r="H439" t="n">
+        <v>0.6269419545369466</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성물산_일별_기준주가.xlsx
+++ b/data/삼성물산_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H439"/>
+  <dimension ref="A1:H440"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11826,6 +11826,32 @@
         <v>0.6269419545369466</v>
       </c>
     </row>
+    <row r="440">
+      <c r="A440" s="1" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B440" t="n">
+        <v>288000</v>
+      </c>
+      <c r="C440" t="n">
+        <v>259570</v>
+      </c>
+      <c r="D440" t="n">
+        <v>341576</v>
+      </c>
+      <c r="E440" t="n">
+        <v>307181</v>
+      </c>
+      <c r="F440" t="n">
+        <v>285846</v>
+      </c>
+      <c r="G440" t="n">
+        <v>311535</v>
+      </c>
+      <c r="H440" t="n">
+        <v>0.6197772601543166</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성물산_일별_기준주가.xlsx
+++ b/data/삼성물산_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H440"/>
+  <dimension ref="A1:H441"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11852,6 +11852,32 @@
         <v>0.6197772601543166</v>
       </c>
     </row>
+    <row r="441">
+      <c r="A441" s="1" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B441" t="n">
+        <v>292000</v>
+      </c>
+      <c r="C441" t="n">
+        <v>285807</v>
+      </c>
+      <c r="D441" t="n">
+        <v>337503</v>
+      </c>
+      <c r="E441" t="n">
+        <v>306545</v>
+      </c>
+      <c r="F441" t="n">
+        <v>287047</v>
+      </c>
+      <c r="G441" t="n">
+        <v>310365</v>
+      </c>
+      <c r="H441" t="n">
+        <v>0.613694029074725</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성물산_일별_기준주가.xlsx
+++ b/data/삼성물산_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H441"/>
+  <dimension ref="A1:H442"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11878,6 +11878,32 @@
         <v>0.613694029074725</v>
       </c>
     </row>
+    <row r="442">
+      <c r="A442" s="1" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B442" t="n">
+        <v>301000</v>
+      </c>
+      <c r="C442" t="n">
+        <v>311788</v>
+      </c>
+      <c r="D442" t="n">
+        <v>335506</v>
+      </c>
+      <c r="E442" t="n">
+        <v>306303</v>
+      </c>
+      <c r="F442" t="n">
+        <v>291634</v>
+      </c>
+      <c r="G442" t="n">
+        <v>311148</v>
+      </c>
+      <c r="H442" t="n">
+        <v>0.6177651144895284</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성물산_일별_기준주가.xlsx
+++ b/data/삼성물산_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H442"/>
+  <dimension ref="A1:H443"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11904,6 +11904,32 @@
         <v>0.6177651144895284</v>
       </c>
     </row>
+    <row r="443">
+      <c r="A443" s="1" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B443" t="n">
+        <v>324500</v>
+      </c>
+      <c r="C443" t="n">
+        <v>419636</v>
+      </c>
+      <c r="D443" t="n">
+        <v>334469</v>
+      </c>
+      <c r="E443" t="n">
+        <v>304633</v>
+      </c>
+      <c r="F443" t="n">
+        <v>299802</v>
+      </c>
+      <c r="G443" t="n">
+        <v>312968</v>
+      </c>
+      <c r="H443" t="n">
+        <v>0.6272279183911154</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성물산_일별_기준주가.xlsx
+++ b/data/삼성물산_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H443"/>
+  <dimension ref="A1:H444"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11930,6 +11930,32 @@
         <v>0.6272279183911154</v>
       </c>
     </row>
+    <row r="444">
+      <c r="A444" s="1" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B444" t="n">
+        <v>323500</v>
+      </c>
+      <c r="C444" t="n">
+        <v>421541</v>
+      </c>
+      <c r="D444" t="n">
+        <v>334134</v>
+      </c>
+      <c r="E444" t="n">
+        <v>304249</v>
+      </c>
+      <c r="F444" t="n">
+        <v>308890</v>
+      </c>
+      <c r="G444" t="n">
+        <v>315757</v>
+      </c>
+      <c r="H444" t="n">
+        <v>0.6417288854688767</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성물산_일별_기준주가.xlsx
+++ b/data/삼성물산_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H444"/>
+  <dimension ref="A1:H445"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11956,6 +11956,32 @@
         <v>0.6417288854688767</v>
       </c>
     </row>
+    <row r="445">
+      <c r="A445" s="1" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B445" t="n">
+        <v>312000</v>
+      </c>
+      <c r="C445" t="n">
+        <v>314343</v>
+      </c>
+      <c r="D445" t="n">
+        <v>333641</v>
+      </c>
+      <c r="E445" t="n">
+        <v>303133</v>
+      </c>
+      <c r="F445" t="n">
+        <v>312540</v>
+      </c>
+      <c r="G445" t="n">
+        <v>316438</v>
+      </c>
+      <c r="H445" t="n">
+        <v>0.6452696379177671</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
